--- a/pasto_case/results/AHP_results/AHP_TOPSIS_results2.xlsx
+++ b/pasto_case/results/AHP_results/AHP_TOPSIS_results2.xlsx
@@ -478,249 +478,249 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01877892212300053</v>
+        <v>0.01878590927456647</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009101349640918275</v>
+        <v>0.009085397741954012</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02077649478575084</v>
+        <v>0.01899433116996889</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001179831106877801</v>
+        <v>0.0004595534968166449</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002493572614815913</v>
+        <v>0.0004731435703355144</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2052201324288195</v>
+        <v>0.1791909340831585</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01154805700284012</v>
+        <v>0.01157825379611231</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05327376232240418</v>
+        <v>0.06069247306037528</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007391264298298317</v>
+        <v>0.007327311748516105</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008306772399082209</v>
+        <v>0.008252430531668815</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05789323952090816</v>
+        <v>0.06948622190603752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05009978663050073</v>
+        <v>0.04508357056276896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004964087133505546</v>
+        <v>0.00680663015679641</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1625041338197434</v>
+        <v>0.1234766547316297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06159793527409946</v>
+        <v>0.0676870106819252</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2748655357050956</v>
+        <v>0.3540788493226166</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01799359797757912</v>
+        <v>0.01798827098942156</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008306772399082209</v>
+        <v>0.008252430531668815</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05789323952090816</v>
+        <v>0.06948622190603752</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05009978663050073</v>
+        <v>0.04508357056276896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004964087133505546</v>
+        <v>0.00680663015679641</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1621045702291284</v>
+        <v>0.1229437481413414</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06250372076507893</v>
+        <v>0.06852143801024103</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2782787780825549</v>
+        <v>0.3578793585795425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01852197798085997</v>
+        <v>0.0185452759645697</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008306772399082209</v>
+        <v>0.008252430531668815</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05602975145722725</v>
+        <v>0.06593759031809104</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05009978663050073</v>
+        <v>0.04508357056276896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004964087133505546</v>
+        <v>0.00680663015679641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1639661717440671</v>
+        <v>0.1264898008016971</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0615088431310936</v>
+        <v>0.06604250665709453</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2727967139292544</v>
+        <v>0.3430203872211412</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01694484119385461</v>
+        <v>0.01697957573715034</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00718331163077789</v>
+        <v>0.007425125564513936</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2199881330424932</v>
+        <v>0.1924243572902395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01341483359705943</v>
+        <v>0.02273430545594346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0007166516589685644</v>
+        <v>0.00101357539818229</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03720681506655017</v>
+        <v>0.02322026150631198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1998160686692217</v>
+        <v>0.1751216628563845</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8430243760428316</v>
+        <v>0.8829281223275296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01715615841965796</v>
+        <v>0.0171475502523592</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008857562792845115</v>
+        <v>0.008836617315334578</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03007954581440301</v>
+        <v>0.02883025772670736</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03177918773041463</v>
+        <v>0.03392900571520543</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006320846233754776</v>
+        <v>0.004304733194441361</v>
       </c>
       <c r="G7" t="n">
-        <v>0.190797556268138</v>
+        <v>0.1640017105451372</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03402773334666263</v>
+        <v>0.03646998979038951</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1513518937525368</v>
+        <v>0.1819208882318561</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01875458373098354</v>
+        <v>0.01875987901896177</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008857562792845115</v>
+        <v>0.008836617315334578</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03007954581440301</v>
+        <v>0.02883025772670736</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03177918773041463</v>
+        <v>0.03392900571520543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006320846233754776</v>
+        <v>0.004304733194441361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1907904039791211</v>
+        <v>0.1639932264881504</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03452040712447425</v>
+        <v>0.03693679284171839</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1532123867265391</v>
+        <v>0.1838291409362724</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01880909484887686</v>
+        <v>0.01881666758756575</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008857562792845115</v>
+        <v>0.008836617315334578</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03007954581440301</v>
+        <v>0.02883025772670736</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03177918773041463</v>
+        <v>0.03392900571520543</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006320846233754776</v>
+        <v>0.004304733194441361</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1907903961918793</v>
+        <v>0.1639932166556052</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03453838927906071</v>
+        <v>0.03695440932602032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1532799691210116</v>
+        <v>0.1839007012175371</v>
       </c>
     </row>
   </sheetData>
